--- a/data/trans_dic/IP12B$estomago-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,07</t>
+          <t>0,0; 50,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,71</t>
+          <t>0,0; 31,01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,42 +788,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,74</t>
+          <t>0,0; 28,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,87</t>
+          <t>0,0; 26,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,87</t>
+          <t>0,0; 25,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,91</t>
+          <t>0,0; 41,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,38</t>
+          <t>0,0; 20,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,54</t>
+          <t>0,0; 12,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -834,7 +835,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,88</t>
+          <t>0,0; 38,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,06</t>
+          <t>0,0; 26,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,7</t>
+          <t>0,0; 24,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,87</t>
+          <t>0,0; 17,93</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,6</t>
+          <t>0,0; 60,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,56</t>
+          <t>0,0; 31,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,77</t>
+          <t>0,0; 65,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,01</t>
+          <t>0,0; 23,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,1</t>
+          <t>0,0; 53,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,77</t>
+          <t>0,0; 23,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,4</t>
+          <t>0,0; 30,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 26,13</t>
+          <t>2,37; 27,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,72</t>
+          <t>0,0; 12,91</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,15</t>
+          <t>1,01; 9,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,7</t>
+          <t>1,01; 9,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,37</t>
+          <t>1,38; 11,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 14,57</t>
+          <t>1,46; 13,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,42</t>
+          <t>1,48; 8,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,3</t>
+          <t>0,48; 4,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,91</t>
+          <t>1,79; 9,16</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5090</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5986</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1270</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2941</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2419</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3516</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3286</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3233</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3152</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3956</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3310</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2579</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3633</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3044</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3225</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2654</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2735</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2294</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3098</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3206</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4169</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>468; 5426</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3078</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1747</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>3584</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>445; 4283</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3991</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>556; 5010</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>642; 5413</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4104</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>700; 6422</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1340; 7752</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>601; 5842</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1840; 9437</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$estomago-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,22</t>
+          <t>0,0; 51,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,01</t>
+          <t>0,0; 32,17</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,54</t>
+          <t>0,0; 25,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,25</t>
+          <t>0,0; 25,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,28</t>
+          <t>0,0; 18,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,04</t>
+          <t>0,0; 34,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,05</t>
+          <t>0,0; 19,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,1</t>
+          <t>0,0; 9,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,97</t>
+          <t>0,0; 27,01</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,78</t>
+          <t>0,0; 35,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,21</t>
+          <t>0,0; 30,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,41</t>
+          <t>0,0; 20,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,93</t>
+          <t>0,0; 14,88</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,45</t>
+          <t>0,0; 58,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,44</t>
+          <t>0,0; 28,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,55</t>
+          <t>0,0; 23,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,39</t>
+          <t>0,0; 53,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,64</t>
+          <t>0,0; 29,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,01</t>
+          <t>0,0; 34,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,37; 27,55</t>
+          <t>3,38; 27,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,91</t>
+          <t>0,0; 15,56</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,76</t>
+          <t>1,02; 9,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,09</t>
+          <t>1,0; 8,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,59</t>
+          <t>1,38; 10,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,42</t>
+          <t>1,48; 15,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,56</t>
+          <t>1,47; 7,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,68</t>
+          <t>0,48; 4,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,16</t>
+          <t>1,48; 8,64</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5090</t>
+          <t>0; 5174</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5986</t>
+          <t>0; 6209</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2941</t>
+          <t>0; 2632</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2419</t>
+          <t>0; 2390</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3516</t>
+          <t>0; 2575</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3286</t>
+          <t>0; 2791</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3233</t>
+          <t>0; 3208</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3152</t>
+          <t>0; 2547</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3956</t>
+          <t>0; 4651</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3310</t>
+          <t>0; 3015</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2579</t>
+          <t>0; 3039</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3633</t>
+          <t>0; 3071</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3500</t>
+          <t>0; 2905</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3044</t>
+          <t>0; 2933</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3225</t>
+          <t>0; 2943</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2735</t>
+          <t>0; 2680</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3206</t>
+          <t>0; 3998</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4169</t>
+          <t>0; 4830</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>468; 5426</t>
+          <t>666; 5436</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3078</t>
+          <t>0; 3710</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>445; 4283</t>
+          <t>447; 3956</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 3991</t>
+          <t>0; 3363</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>556; 5010</t>
+          <t>549; 4661</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>642; 5413</t>
+          <t>643; 4849</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>0; 4514</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>700; 6422</t>
+          <t>708; 7410</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1340; 7752</t>
+          <t>1329; 7216</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>601; 5842</t>
+          <t>605; 5908</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1840; 9437</t>
+          <t>1520; 8903</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$estomago-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 51,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,17</t>
+          <t>0,0; 28,71</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,22%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,19%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 22,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,94</t>
+          <t>0,0; 42,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 25,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,86</t>
+          <t>0,0; 26,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,89</t>
+          <t>0,0; 16,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,78</t>
+          <t>0,0; 9,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,01</t>
+          <t>0,0; 22,97</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,69%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 36,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,63</t>
+          <t>0,0; 19,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,88</t>
+          <t>0,0; 15,87</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 58,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,7</t>
+          <t>0,0; 31,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 66,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,08</t>
+          <t>0,0; 28,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>15,63%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>4,55%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,38</t>
+          <t>0,0; 29,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,77</t>
+          <t>0,0; 52,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 19,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 27,6</t>
+          <t>3,38; 26,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,56</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,53%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>3,17%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,02</t>
+          <t>1,38; 10,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,46</t>
+          <t>1,47; 14,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,38</t>
+          <t>1,0; 9,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 15,48</t>
+          <t>1,0; 8,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,97</t>
+          <t>1,48; 8,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,73</t>
+          <t>0,48; 4,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,64</t>
+          <t>1,48; 8,91</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5177</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5174</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6209</t>
+          <t>0; 5542</t>
         </is>
       </c>
     </row>
@@ -1918,14 +1918,14 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>571</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2632</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3181</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2390</t>
+          <t>0; 3435</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2653</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2575</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2791</t>
+          <t>0; 2476</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3208</t>
+          <t>0; 2642</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2547</t>
+          <t>0; 2484</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4651</t>
+          <t>0; 3955</t>
         </is>
       </c>
     </row>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2302,27 +2302,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>560</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3039</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3148</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2959</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3071</t>
+          <t>0; 2933</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2905</t>
+          <t>0; 3099</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>731</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2950</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2933</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2943</t>
+          <t>0; 3237</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>650</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2700</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2680</t>
+          <t>0; 3253</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>907</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1387</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3098</t>
+          <t>0; 4085</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3998</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4830</t>
+          <t>0; 3024</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2681</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>666; 5436</t>
+          <t>667; 5147</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 3710</t>
+          <t>0; 3031</t>
         </is>
       </c>
     </row>
@@ -3064,22 +3064,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>1548</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1747</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>447; 3956</t>
+          <t>643; 4841</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 3363</t>
+          <t>0; 4478</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>549; 4661</t>
+          <t>705; 6971</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>643; 4849</t>
+          <t>440; 4013</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 4514</t>
+          <t>0; 2934</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>708; 7410</t>
+          <t>550; 4798</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1329; 7216</t>
+          <t>1336; 7631</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>605; 5908</t>
+          <t>603; 5364</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1520; 8903</t>
+          <t>1520; 9176</t>
         </is>
       </c>
     </row>
